--- a/organization-server/src/main/resources/Import_template.xlsx
+++ b/organization-server/src/main/resources/Import_template.xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+    <workbookView windowHeight="21900"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="153">
   <si>
     <t>填表说明：
 1. 千万不要修改表结构，只能填写下面空格和增加行数，不要删除此说明行和表头行，不要删除列和新加列；
@@ -71,6 +87,9 @@
     <t>级别</t>
   </si>
   <si>
+    <t>登录密码</t>
+  </si>
+  <si>
     <t>刘备</t>
   </si>
   <si>
@@ -482,53 +501,203 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="0" formatCode="General"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="等线"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="8"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color indexed="9"/>
       <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="14"/>
       <color indexed="9"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color indexed="13"/>
       <name val="Microsoft YaHei"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="13"/>
       <color indexed="14"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Helvetica Neue"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica Neue"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -538,23 +707,209 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="9"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="11"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="12"/>
-        <bgColor auto="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -580,22 +935,6 @@
         <color indexed="10"/>
       </left>
       <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -628,109 +967,452 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="bottom" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0"/>
   <colors>
     <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ff70ad47"/>
-      <rgbColor rgb="ffc00000"/>
-      <rgbColor rgb="ff112233"/>
-      <rgbColor rgb="ff333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00AAAAAA"/>
+      <rgbColor rgb="0070AD47"/>
+      <rgbColor rgb="00C00000"/>
+      <rgbColor rgb="00112233"/>
+      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
+<customStorage xmlns="https://web.wps.cn/et/2018/main">
+  <book/>
+  <sheets/>
+</customStorage>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
     <a:clrScheme name="Office 主题​​">
       <a:dk1>
@@ -929,8 +1611,6 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
@@ -950,8 +1630,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -963,7 +1642,7 @@
             <a:latin typeface="+mn-lt"/>
             <a:ea typeface="+mn-ea"/>
             <a:cs typeface="+mn-cs"/>
-            <a:sym typeface="Helvetica Neue"/>
+            <a:sym typeface="Helvetica Neue" panose="02000503000000020004"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -980,8 +1659,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1006,8 +1684,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1032,8 +1709,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1058,8 +1734,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1084,8 +1759,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1110,8 +1784,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1136,8 +1809,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1162,8 +1834,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1188,8 +1859,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1202,9 +1872,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
@@ -1218,8 +1894,6 @@
           <a:prstDash val="solid"/>
           <a:round/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:noAutofit/>
@@ -1239,8 +1913,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1265,8 +1938,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1291,8 +1963,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1317,8 +1988,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1343,8 +2013,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1369,8 +2038,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1395,8 +2063,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1421,8 +2088,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1447,8 +2113,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1473,8 +2138,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1487,9 +2151,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
@@ -1500,8 +2170,6 @@
           <a:noFill/>
           <a:miter lim="400000"/>
         </a:ln>
-        <a:effectLst/>
-        <a:sp3d/>
       </a:spPr>
       <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
@@ -1521,8 +2189,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1100" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1534,7 +2201,7 @@
             <a:latin typeface="+mn-lt"/>
             <a:ea typeface="+mn-ea"/>
             <a:cs typeface="+mn-cs"/>
-            <a:sym typeface="Helvetica Neue"/>
+            <a:sym typeface="Helvetica Neue" panose="02000503000000020004"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1551,8 +2218,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1577,8 +2243,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1603,8 +2268,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1629,8 +2293,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1655,8 +2318,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1681,8 +2343,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1707,8 +2368,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1733,8 +2393,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1759,8 +2418,7 @@
           <a:buSzTx/>
           <a:buFontTx/>
           <a:buNone/>
-          <a:tabLst/>
-          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+          <a:defRPr kumimoji="0" sz="1800" b="0" i="0" u="none" strike="noStrike" cap="none" spc="0" normalizeH="0" baseline="0">
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1773,9 +2431,15 @@
         </a:lvl9pPr>
       </a:lstStyle>
       <a:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
+        <a:lnRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:srgbClr val="FFFFFF"/>
+        </a:effectRef>
         <a:fontRef idx="none"/>
       </a:style>
     </a:txDef>
@@ -1784,28 +2448,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:O33"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
-    <col min="2" max="2" width="16.3516" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.35" style="1" customWidth="1"/>
     <col min="3" max="3" width="16.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="26.3516" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.35" style="1" customWidth="1"/>
     <col min="5" max="5" width="67" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.3516" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.35" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.5" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.8516" style="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6719" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.6719" style="1" customWidth="1"/>
-    <col min="11" max="13" width="12.6719" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.5" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="8" max="8" width="13.85" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.675" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.675" style="1" customWidth="1"/>
+    <col min="11" max="13" width="12.675" style="1" customWidth="1"/>
+    <col min="14" max="15" width="16" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15.55" style="1" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="205.55" customHeight="1">
-      <c r="A1" t="s" s="2">
+    <row r="1" ht="205.55" customHeight="1" spans="1:16">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3"/>
@@ -1820,1281 +2485,1378 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="4"/>
-      <c r="O1" s="4"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
     </row>
-    <row r="2" ht="19.25" customHeight="1">
-      <c r="A2" t="s" s="5">
+    <row r="2" ht="19.25" customHeight="1" spans="1:16">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" t="s" s="6">
+      <c r="B2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s" s="6">
+      <c r="C2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s" s="7">
+      <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" t="s" s="6">
+      <c r="E2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F2" t="s" s="7">
+      <c r="F2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s" s="7">
+      <c r="G2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H2" t="s" s="7">
+      <c r="H2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="I2" t="s" s="7">
+      <c r="I2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" t="s" s="7">
+      <c r="J2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="K2" t="s" s="7">
+      <c r="K2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="L2" t="s" s="7">
+      <c r="L2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="M2" t="s" s="7">
+      <c r="M2" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="N2" t="s" s="7">
+      <c r="N2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="O2" t="s" s="8">
+      <c r="O2" s="17" t="s">
         <v>15</v>
       </c>
+      <c r="P2" s="17" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="3" ht="16.75" customHeight="1">
-      <c r="A3" s="9"/>
-      <c r="B3" t="s" s="10">
-        <v>16</v>
-      </c>
-      <c r="C3" s="11">
+    <row r="3" ht="16.75" customHeight="1" spans="1:16">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="9">
         <v>13900000001</v>
       </c>
-      <c r="D3" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s" s="12">
+      <c r="D3" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="11">
+      <c r="E3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="9">
         <v>1</v>
       </c>
-      <c r="G3" t="s" s="12">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s" s="13">
+      <c r="G3" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="I3" t="s" s="12">
+      <c r="H3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J3" t="s" s="12">
+      <c r="I3" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" t="s" s="12">
+      <c r="J3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="N3" t="s" s="14">
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O3" s="15">
+      <c r="N3" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="O3" s="19">
         <v>10</v>
       </c>
+      <c r="P3" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" t="s" s="17">
-        <v>25</v>
-      </c>
-      <c r="C4" s="18">
+    <row r="4" ht="17" customHeight="1" spans="1:16">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="13">
         <v>13900000002</v>
       </c>
-      <c r="D4" t="s" s="17">
-        <v>26</v>
-      </c>
-      <c r="E4" t="s" s="17">
+      <c r="D4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="18">
+      <c r="E4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4" s="13">
         <v>2</v>
       </c>
-      <c r="G4" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H4" t="s" s="19">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J4" t="s" s="17">
+      <c r="G4" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" t="s" s="17">
+      <c r="I4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="N4" t="s" s="20">
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="12" t="s">
         <v>31</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="O4" s="21">
         <v>8</v>
       </c>
+      <c r="P4" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="16"/>
-      <c r="B5" t="s" s="17">
-        <v>32</v>
-      </c>
-      <c r="C5" s="18">
+    <row r="5" ht="17" customHeight="1" spans="1:16">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="13">
         <v>13900000003</v>
       </c>
-      <c r="D5" t="s" s="17">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s" s="17">
+      <c r="D5" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="18">
+      <c r="E5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="13">
         <v>3</v>
       </c>
-      <c r="G5" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H5" t="s" s="19">
-        <v>35</v>
-      </c>
-      <c r="I5" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J5" t="s" s="17">
-        <v>29</v>
-      </c>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" t="s" s="17">
+      <c r="G5" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="N5" t="s" s="20">
+      <c r="I5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="12" t="s">
         <v>37</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>38</v>
       </c>
       <c r="O5" s="21">
         <v>8</v>
       </c>
+      <c r="P5" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="16"/>
-      <c r="B6" t="s" s="17">
-        <v>38</v>
-      </c>
-      <c r="C6" s="18">
+    <row r="6" ht="17" customHeight="1" spans="1:16">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="13">
         <v>13900000004</v>
       </c>
-      <c r="D6" t="s" s="17">
-        <v>39</v>
-      </c>
-      <c r="E6" t="s" s="17">
+      <c r="D6" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="18">
+      <c r="E6" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="13">
         <v>4</v>
       </c>
-      <c r="G6" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H6" t="s" s="17">
-        <v>41</v>
-      </c>
-      <c r="I6" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J6" t="s" s="17">
-        <v>29</v>
-      </c>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
-      <c r="M6" t="s" s="17">
+      <c r="G6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="N6" t="s" s="20">
+      <c r="I6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="12" t="s">
         <v>43</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>44</v>
       </c>
       <c r="O6" s="21">
         <v>7</v>
       </c>
+      <c r="P6" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="16"/>
-      <c r="B7" t="s" s="17">
-        <v>44</v>
-      </c>
-      <c r="C7" s="18">
+    <row r="7" ht="17" customHeight="1" spans="1:16">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="13">
         <v>13900000005</v>
       </c>
-      <c r="D7" t="s" s="17">
-        <v>45</v>
-      </c>
-      <c r="E7" t="s" s="17">
+      <c r="D7" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F7" s="18">
+      <c r="E7" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="13">
         <v>5</v>
       </c>
-      <c r="G7" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H7" t="s" s="17">
-        <v>47</v>
-      </c>
-      <c r="I7" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J7" t="s" s="17">
+      <c r="G7" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="16"/>
-      <c r="L7" s="16"/>
-      <c r="M7" t="s" s="17">
-        <v>48</v>
-      </c>
-      <c r="N7" t="s" s="20">
+      <c r="J7" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="12" t="s">
         <v>49</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>50</v>
       </c>
       <c r="O7" s="21">
         <v>7</v>
       </c>
+      <c r="P7" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="16"/>
-      <c r="B8" t="s" s="17">
-        <v>50</v>
-      </c>
-      <c r="C8" s="18">
+    <row r="8" ht="17" customHeight="1" spans="1:16">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="13">
         <v>13900000006</v>
       </c>
-      <c r="D8" t="s" s="17">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s" s="17">
+      <c r="D8" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="18">
+      <c r="E8" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="13">
         <v>6</v>
       </c>
-      <c r="G8" t="s" s="17">
-        <v>53</v>
-      </c>
-      <c r="H8" s="16"/>
-      <c r="I8" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J8" t="s" s="17">
+      <c r="G8" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H8" s="11"/>
+      <c r="I8" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="16"/>
-      <c r="L8" s="16"/>
-      <c r="M8" t="s" s="17">
-        <v>54</v>
-      </c>
-      <c r="N8" t="s" s="20">
+      <c r="J8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="12" t="s">
         <v>55</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>56</v>
       </c>
       <c r="O8" s="21">
         <v>7</v>
       </c>
+      <c r="P8" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="16"/>
-      <c r="B9" t="s" s="17">
-        <v>56</v>
-      </c>
-      <c r="C9" s="18">
+    <row r="9" ht="17" customHeight="1" spans="1:16">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="13">
         <v>13900000007</v>
       </c>
-      <c r="D9" t="s" s="17">
-        <v>57</v>
-      </c>
-      <c r="E9" t="s" s="17">
+      <c r="D9" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="18">
+      <c r="E9" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="13">
         <v>7</v>
       </c>
-      <c r="G9" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H9" s="16"/>
-      <c r="I9" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J9" t="s" s="17">
+      <c r="G9" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="11"/>
+      <c r="I9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K9" s="16"/>
-      <c r="L9" s="16"/>
-      <c r="M9" t="s" s="17">
-        <v>59</v>
-      </c>
-      <c r="N9" t="s" s="20">
+      <c r="J9" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="12" t="s">
         <v>60</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>61</v>
       </c>
       <c r="O9" s="21">
         <v>7</v>
       </c>
+      <c r="P9" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="16"/>
-      <c r="B10" t="s" s="17">
-        <v>61</v>
-      </c>
-      <c r="C10" s="18">
+    <row r="10" ht="17" customHeight="1" spans="1:16">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="13">
         <v>13900000008</v>
       </c>
-      <c r="D10" t="s" s="17">
-        <v>62</v>
-      </c>
-      <c r="E10" t="s" s="17">
+      <c r="D10" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="18">
+      <c r="E10" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="13">
         <v>8</v>
       </c>
-      <c r="G10" t="s" s="17">
-        <v>53</v>
-      </c>
-      <c r="H10" s="16"/>
-      <c r="I10" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J10" t="s" s="17">
+      <c r="G10" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="11"/>
+      <c r="I10" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K10" s="16"/>
-      <c r="L10" s="16"/>
-      <c r="M10" t="s" s="17">
-        <v>64</v>
-      </c>
-      <c r="N10" t="s" s="20">
+      <c r="J10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="12" t="s">
         <v>65</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>66</v>
       </c>
       <c r="O10" s="21">
         <v>3</v>
       </c>
+      <c r="P10" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="16"/>
-      <c r="B11" t="s" s="17">
-        <v>66</v>
-      </c>
-      <c r="C11" s="18">
+    <row r="11" ht="17" customHeight="1" spans="1:16">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="13">
         <v>13900000009</v>
       </c>
-      <c r="D11" t="s" s="17">
-        <v>67</v>
-      </c>
-      <c r="E11" t="s" s="17">
+      <c r="D11" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="F11" s="18">
+      <c r="E11" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="F11" s="13">
         <v>9</v>
       </c>
-      <c r="G11" t="s" s="17">
-        <v>53</v>
-      </c>
-      <c r="H11" s="16"/>
-      <c r="I11" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J11" t="s" s="17">
+      <c r="G11" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H11" s="11"/>
+      <c r="I11" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="16"/>
-      <c r="L11" s="16"/>
-      <c r="M11" t="s" s="17">
-        <v>69</v>
-      </c>
-      <c r="N11" t="s" s="20">
+      <c r="J11" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="12" t="s">
         <v>70</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>71</v>
       </c>
       <c r="O11" s="21">
         <v>4</v>
       </c>
+      <c r="P11" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="16"/>
-      <c r="B12" t="s" s="17">
-        <v>71</v>
-      </c>
-      <c r="C12" s="18">
+    <row r="12" ht="17" customHeight="1" spans="1:16">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="13">
         <v>13900000010</v>
       </c>
-      <c r="D12" t="s" s="17">
-        <v>72</v>
-      </c>
-      <c r="E12" t="s" s="17">
+      <c r="D12" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="18">
+      <c r="E12" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="13">
         <v>10</v>
       </c>
-      <c r="G12" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H12" s="16"/>
-      <c r="I12" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J12" t="s" s="17">
+      <c r="G12" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="11"/>
+      <c r="I12" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" t="s" s="17">
-        <v>74</v>
-      </c>
-      <c r="N12" t="s" s="20">
+      <c r="J12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="12" t="s">
         <v>75</v>
+      </c>
+      <c r="N12" s="20" t="s">
+        <v>76</v>
       </c>
       <c r="O12" s="21">
         <v>4</v>
       </c>
+      <c r="P12" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" t="s" s="17">
-        <v>76</v>
-      </c>
-      <c r="C13" s="18">
+    <row r="13" ht="17" customHeight="1" spans="1:16">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="13">
         <v>13900000011</v>
       </c>
-      <c r="D13" t="s" s="17">
-        <v>77</v>
-      </c>
-      <c r="E13" t="s" s="17">
+      <c r="D13" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="18">
+      <c r="E13" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F13" s="13">
         <v>11</v>
       </c>
-      <c r="G13" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H13" s="16"/>
-      <c r="I13" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J13" t="s" s="17">
+      <c r="G13" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K13" s="16"/>
-      <c r="L13" s="16"/>
-      <c r="M13" t="s" s="17">
-        <v>79</v>
-      </c>
-      <c r="N13" t="s" s="20">
+      <c r="J13" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="12" t="s">
         <v>80</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="O13" s="21">
         <v>5</v>
       </c>
+      <c r="P13" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="16"/>
-      <c r="B14" t="s" s="17">
+    <row r="14" ht="17" customHeight="1" spans="1:16">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C14" s="13">
+        <v>13900000012</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="13">
+        <v>12</v>
+      </c>
+      <c r="G14" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K14" s="11"/>
+      <c r="L14" s="11"/>
+      <c r="M14" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="N14" s="20" t="s">
         <v>81</v>
-      </c>
-      <c r="C14" s="18">
-        <v>13900000012</v>
-      </c>
-      <c r="D14" t="s" s="17">
-        <v>82</v>
-      </c>
-      <c r="E14" t="s" s="17">
-        <v>83</v>
-      </c>
-      <c r="F14" s="18">
-        <v>12</v>
-      </c>
-      <c r="G14" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H14" s="16"/>
-      <c r="I14" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J14" t="s" s="17">
-        <v>22</v>
-      </c>
-      <c r="K14" s="16"/>
-      <c r="L14" s="16"/>
-      <c r="M14" t="s" s="17">
-        <v>84</v>
-      </c>
-      <c r="N14" t="s" s="20">
-        <v>80</v>
       </c>
       <c r="O14" s="21">
         <v>3</v>
       </c>
+      <c r="P14" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="16"/>
-      <c r="B15" t="s" s="17">
-        <v>85</v>
-      </c>
-      <c r="C15" s="18">
+    <row r="15" ht="17" customHeight="1" spans="1:16">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="13">
         <v>13900000013</v>
       </c>
-      <c r="D15" t="s" s="17">
-        <v>86</v>
-      </c>
-      <c r="E15" t="s" s="17">
+      <c r="D15" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F15" s="18">
+      <c r="E15" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="F15" s="13">
         <v>13</v>
       </c>
-      <c r="G15" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H15" s="16"/>
-      <c r="I15" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J15" t="s" s="17">
+      <c r="G15" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="16"/>
-      <c r="L15" s="16"/>
-      <c r="M15" t="s" s="17">
-        <v>88</v>
-      </c>
-      <c r="N15" t="s" s="20">
-        <v>80</v>
+      <c r="J15" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>81</v>
       </c>
       <c r="O15" s="21">
         <v>3</v>
       </c>
+      <c r="P15" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="16"/>
-      <c r="B16" t="s" s="17">
-        <v>89</v>
-      </c>
-      <c r="C16" s="18">
+    <row r="16" ht="17" customHeight="1" spans="1:16">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" s="13">
         <v>13900000014</v>
       </c>
-      <c r="D16" t="s" s="17">
-        <v>90</v>
-      </c>
-      <c r="E16" t="s" s="17">
+      <c r="D16" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="F16" s="18">
+      <c r="E16" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F16" s="13">
         <v>14</v>
       </c>
-      <c r="G16" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H16" s="16"/>
-      <c r="I16" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J16" t="s" s="17">
+      <c r="G16" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K16" s="16"/>
-      <c r="L16" s="16"/>
-      <c r="M16" t="s" s="17">
-        <v>92</v>
-      </c>
-      <c r="N16" t="s" s="20">
+      <c r="J16" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="12" t="s">
         <v>93</v>
+      </c>
+      <c r="N16" s="20" t="s">
+        <v>94</v>
       </c>
       <c r="O16" s="21">
         <v>3</v>
       </c>
+      <c r="P16" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="16"/>
-      <c r="B17" t="s" s="17">
+    <row r="17" ht="17" customHeight="1" spans="1:16">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="13">
+        <v>13900000015</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F17" s="13">
+        <v>15</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N17" s="20" t="s">
         <v>94</v>
-      </c>
-      <c r="C17" s="18">
-        <v>13900000015</v>
-      </c>
-      <c r="D17" t="s" s="17">
-        <v>95</v>
-      </c>
-      <c r="E17" t="s" s="17">
-        <v>96</v>
-      </c>
-      <c r="F17" s="18">
-        <v>15</v>
-      </c>
-      <c r="G17" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H17" s="16"/>
-      <c r="I17" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J17" t="s" s="17">
-        <v>22</v>
-      </c>
-      <c r="K17" s="16"/>
-      <c r="L17" s="16"/>
-      <c r="M17" t="s" s="17">
-        <v>97</v>
-      </c>
-      <c r="N17" t="s" s="20">
-        <v>93</v>
       </c>
       <c r="O17" s="21">
         <v>3</v>
       </c>
+      <c r="P17" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="16"/>
-      <c r="B18" t="s" s="17">
-        <v>98</v>
-      </c>
-      <c r="C18" s="18">
+    <row r="18" ht="17" customHeight="1" spans="1:16">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="13">
         <v>13900000016</v>
       </c>
-      <c r="D18" t="s" s="17">
-        <v>99</v>
-      </c>
-      <c r="E18" t="s" s="17">
+      <c r="D18" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="F18" s="18">
+      <c r="E18" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="F18" s="13">
         <v>16</v>
       </c>
-      <c r="G18" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H18" s="16"/>
-      <c r="I18" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J18" t="s" s="17">
+      <c r="G18" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" t="s" s="17">
-        <v>101</v>
-      </c>
-      <c r="N18" t="s" s="20">
+      <c r="J18" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K18" s="11"/>
+      <c r="L18" s="11"/>
+      <c r="M18" s="12" t="s">
         <v>102</v>
+      </c>
+      <c r="N18" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="O18" s="21">
         <v>1</v>
       </c>
+      <c r="P18" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="16"/>
-      <c r="B19" t="s" s="17">
+    <row r="19" ht="17" customHeight="1" spans="1:16">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="13">
+        <v>13900000017</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F19" s="13">
+        <v>17</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="K19" s="11"/>
+      <c r="L19" s="11"/>
+      <c r="M19" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="N19" s="20" t="s">
         <v>103</v>
-      </c>
-      <c r="C19" s="18">
-        <v>13900000017</v>
-      </c>
-      <c r="D19" t="s" s="17">
-        <v>104</v>
-      </c>
-      <c r="E19" t="s" s="17">
-        <v>105</v>
-      </c>
-      <c r="F19" s="18">
-        <v>17</v>
-      </c>
-      <c r="G19" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H19" s="16"/>
-      <c r="I19" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J19" t="s" s="17">
-        <v>22</v>
-      </c>
-      <c r="K19" s="16"/>
-      <c r="L19" s="16"/>
-      <c r="M19" t="s" s="17">
-        <v>106</v>
-      </c>
-      <c r="N19" t="s" s="20">
-        <v>102</v>
       </c>
       <c r="O19" s="21">
         <v>1</v>
       </c>
+      <c r="P19" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="16"/>
-      <c r="B20" t="s" s="17">
-        <v>107</v>
-      </c>
-      <c r="C20" s="18">
+    <row r="20" ht="17" customHeight="1" spans="1:16">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="13">
         <v>13900000018</v>
       </c>
-      <c r="D20" t="s" s="17">
-        <v>108</v>
-      </c>
-      <c r="E20" t="s" s="17">
+      <c r="D20" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="F20" s="18">
+      <c r="E20" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="13">
         <v>18</v>
       </c>
-      <c r="G20" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H20" s="16"/>
-      <c r="I20" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J20" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K20" s="16"/>
-      <c r="L20" s="16"/>
-      <c r="M20" t="s" s="17">
+      <c r="G20" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="11"/>
+      <c r="I20" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="N20" t="s" s="20">
-        <v>102</v>
+      <c r="K20" s="11"/>
+      <c r="L20" s="11"/>
+      <c r="M20" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="N20" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="O20" s="21">
         <v>1</v>
       </c>
+      <c r="P20" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="16"/>
-      <c r="B21" t="s" s="17">
-        <v>112</v>
-      </c>
-      <c r="C21" s="18">
+    <row r="21" ht="17" customHeight="1" spans="1:16">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="13">
         <v>13900000019</v>
       </c>
-      <c r="D21" t="s" s="17">
-        <v>113</v>
-      </c>
-      <c r="E21" t="s" s="17">
-        <v>109</v>
-      </c>
-      <c r="F21" s="18">
+      <c r="D21" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="13">
         <v>19</v>
       </c>
-      <c r="G21" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H21" s="16"/>
-      <c r="I21" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J21" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="16"/>
-      <c r="M21" t="s" s="17">
-        <v>114</v>
-      </c>
-      <c r="N21" t="s" s="20">
-        <v>102</v>
+      <c r="G21" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="11"/>
+      <c r="I21" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K21" s="11"/>
+      <c r="L21" s="11"/>
+      <c r="M21" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="N21" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="O21" s="21">
         <v>1</v>
       </c>
+      <c r="P21" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="16"/>
-      <c r="B22" t="s" s="17">
-        <v>115</v>
-      </c>
-      <c r="C22" s="18">
+    <row r="22" ht="17" customHeight="1" spans="1:16">
+      <c r="A22" s="11"/>
+      <c r="B22" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C22" s="13">
         <v>13900000020</v>
       </c>
-      <c r="D22" t="s" s="17">
-        <v>116</v>
-      </c>
-      <c r="E22" t="s" s="17">
-        <v>52</v>
-      </c>
-      <c r="F22" s="18">
+      <c r="D22" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F22" s="13">
         <v>20</v>
       </c>
-      <c r="G22" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H22" s="16"/>
-      <c r="I22" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J22" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K22" s="16"/>
-      <c r="L22" s="16"/>
-      <c r="M22" t="s" s="17">
-        <v>117</v>
-      </c>
-      <c r="N22" t="s" s="20">
-        <v>102</v>
+      <c r="G22" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K22" s="11"/>
+      <c r="L22" s="11"/>
+      <c r="M22" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="N22" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="O22" s="21">
         <v>1</v>
       </c>
+      <c r="P22" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="16"/>
-      <c r="B23" t="s" s="17">
-        <v>118</v>
-      </c>
-      <c r="C23" s="18">
+    <row r="23" ht="17" customHeight="1" spans="1:16">
+      <c r="A23" s="11"/>
+      <c r="B23" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C23" s="13">
         <v>13900000021</v>
       </c>
-      <c r="D23" t="s" s="17">
-        <v>119</v>
-      </c>
-      <c r="E23" t="s" s="17">
-        <v>52</v>
-      </c>
-      <c r="F23" s="18">
+      <c r="D23" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="F23" s="13">
         <v>21</v>
       </c>
-      <c r="G23" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H23" s="16"/>
-      <c r="I23" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J23" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K23" s="16"/>
-      <c r="L23" s="16"/>
-      <c r="M23" t="s" s="17">
-        <v>120</v>
-      </c>
-      <c r="N23" t="s" s="20">
-        <v>102</v>
+      <c r="G23" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="11"/>
+      <c r="I23" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" s="11"/>
+      <c r="L23" s="11"/>
+      <c r="M23" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="N23" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="O23" s="21">
         <v>1</v>
       </c>
+      <c r="P23" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="16"/>
-      <c r="B24" t="s" s="17">
-        <v>121</v>
-      </c>
-      <c r="C24" s="18">
+    <row r="24" ht="17" customHeight="1" spans="1:16">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="13">
         <v>13900000022</v>
       </c>
-      <c r="D24" t="s" s="17">
-        <v>122</v>
-      </c>
-      <c r="E24" t="s" s="17">
-        <v>46</v>
-      </c>
-      <c r="F24" s="18">
+      <c r="D24" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="13">
         <v>22</v>
       </c>
-      <c r="G24" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H24" s="16"/>
-      <c r="I24" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J24" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
-      <c r="L24" s="16"/>
-      <c r="M24" t="s" s="17">
-        <v>123</v>
-      </c>
-      <c r="N24" t="s" s="20">
-        <v>102</v>
+      <c r="G24" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="O24" s="21">
         <v>1</v>
       </c>
+      <c r="P24" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="16"/>
-      <c r="B25" t="s" s="17">
-        <v>124</v>
-      </c>
-      <c r="C25" s="18">
+    <row r="25" ht="17" customHeight="1" spans="1:16">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="13">
         <v>13900000023</v>
       </c>
-      <c r="D25" t="s" s="17">
-        <v>125</v>
-      </c>
-      <c r="E25" t="s" s="17">
-        <v>46</v>
-      </c>
-      <c r="F25" s="18">
+      <c r="D25" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="13">
         <v>23</v>
       </c>
-      <c r="G25" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H25" s="16"/>
-      <c r="I25" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J25" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K25" s="16"/>
-      <c r="L25" s="16"/>
-      <c r="M25" t="s" s="17">
-        <v>126</v>
-      </c>
-      <c r="N25" t="s" s="20">
-        <v>102</v>
+      <c r="G25" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="11"/>
+      <c r="I25" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="N25" s="20" t="s">
+        <v>103</v>
       </c>
       <c r="O25" s="21">
         <v>1</v>
       </c>
+      <c r="P25" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="16"/>
-      <c r="B26" t="s" s="17">
-        <v>127</v>
-      </c>
-      <c r="C26" s="18">
+    <row r="26" ht="17" customHeight="1" spans="1:16">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C26" s="13">
         <v>13900000024</v>
       </c>
-      <c r="D26" t="s" s="17">
-        <v>128</v>
-      </c>
-      <c r="E26" t="s" s="17">
-        <v>78</v>
-      </c>
-      <c r="F26" s="18">
+      <c r="D26" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F26" s="13">
         <v>24</v>
       </c>
-      <c r="G26" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H26" s="16"/>
-      <c r="I26" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J26" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K26" s="16"/>
-      <c r="L26" s="16"/>
-      <c r="M26" t="s" s="17">
-        <v>129</v>
-      </c>
-      <c r="N26" t="s" s="20">
+      <c r="G26" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="11"/>
+      <c r="I26" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="12" t="s">
         <v>130</v>
+      </c>
+      <c r="N26" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="O26" s="21">
         <v>1</v>
       </c>
+      <c r="P26" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="16"/>
-      <c r="B27" t="s" s="17">
+    <row r="27" ht="17" customHeight="1" spans="1:16">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C27" s="13">
+        <v>13900000025</v>
+      </c>
+      <c r="D27" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="F27" s="13">
+        <v>25</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="11"/>
+      <c r="I27" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K27" s="11"/>
+      <c r="L27" s="11"/>
+      <c r="M27" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="N27" s="20" t="s">
         <v>131</v>
-      </c>
-      <c r="C27" s="18">
-        <v>13900000025</v>
-      </c>
-      <c r="D27" t="s" s="17">
-        <v>132</v>
-      </c>
-      <c r="E27" t="s" s="17">
-        <v>78</v>
-      </c>
-      <c r="F27" s="18">
-        <v>25</v>
-      </c>
-      <c r="G27" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H27" s="16"/>
-      <c r="I27" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J27" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K27" s="16"/>
-      <c r="L27" s="16"/>
-      <c r="M27" t="s" s="17">
-        <v>133</v>
-      </c>
-      <c r="N27" t="s" s="20">
-        <v>130</v>
       </c>
       <c r="O27" s="21">
         <v>1</v>
       </c>
+      <c r="P27" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="16"/>
-      <c r="B28" t="s" s="17">
-        <v>134</v>
-      </c>
-      <c r="C28" s="18">
+    <row r="28" ht="17" customHeight="1" spans="1:16">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="13">
         <v>13900000026</v>
       </c>
-      <c r="D28" t="s" s="17">
-        <v>135</v>
-      </c>
-      <c r="E28" t="s" s="17">
-        <v>83</v>
-      </c>
-      <c r="F28" s="18">
+      <c r="D28" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="13">
         <v>26</v>
       </c>
-      <c r="G28" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H28" s="16"/>
-      <c r="I28" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J28" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K28" s="16"/>
-      <c r="L28" s="16"/>
-      <c r="M28" t="s" s="17">
-        <v>136</v>
-      </c>
-      <c r="N28" t="s" s="20">
-        <v>130</v>
+      <c r="G28" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="11"/>
+      <c r="I28" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K28" s="11"/>
+      <c r="L28" s="11"/>
+      <c r="M28" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="N28" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="O28" s="21">
         <v>2</v>
       </c>
+      <c r="P28" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="16"/>
-      <c r="B29" t="s" s="17">
-        <v>137</v>
-      </c>
-      <c r="C29" s="18">
+    <row r="29" ht="17" customHeight="1" spans="1:16">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C29" s="13">
         <v>13900000027</v>
       </c>
-      <c r="D29" t="s" s="17">
-        <v>138</v>
-      </c>
-      <c r="E29" t="s" s="17">
-        <v>83</v>
-      </c>
-      <c r="F29" s="18">
+      <c r="D29" s="12" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" s="13">
         <v>27</v>
       </c>
-      <c r="G29" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H29" s="16"/>
-      <c r="I29" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J29" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K29" s="16"/>
-      <c r="L29" s="16"/>
-      <c r="M29" t="s" s="17">
-        <v>139</v>
-      </c>
-      <c r="N29" t="s" s="20">
-        <v>130</v>
+      <c r="G29" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="11"/>
+      <c r="I29" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J29" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K29" s="11"/>
+      <c r="L29" s="11"/>
+      <c r="M29" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="N29" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="O29" s="21">
         <v>2</v>
       </c>
+      <c r="P29" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="16"/>
-      <c r="B30" t="s" s="17">
-        <v>140</v>
-      </c>
-      <c r="C30" s="18">
+    <row r="30" ht="17" customHeight="1" spans="1:16">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C30" s="13">
         <v>13900000028</v>
       </c>
-      <c r="D30" t="s" s="17">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s" s="17">
-        <v>91</v>
-      </c>
-      <c r="F30" s="18">
+      <c r="D30" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F30" s="13">
         <v>28</v>
       </c>
-      <c r="G30" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H30" s="16"/>
-      <c r="I30" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J30" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K30" s="16"/>
-      <c r="L30" s="16"/>
-      <c r="M30" t="s" s="17">
-        <v>142</v>
-      </c>
-      <c r="N30" t="s" s="20">
-        <v>130</v>
+      <c r="G30" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="11"/>
+      <c r="I30" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K30" s="11"/>
+      <c r="L30" s="11"/>
+      <c r="M30" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="N30" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="O30" s="21">
         <v>1</v>
       </c>
+      <c r="P30" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="16"/>
-      <c r="B31" t="s" s="17">
-        <v>143</v>
-      </c>
-      <c r="C31" s="18">
+    <row r="31" ht="17" customHeight="1" spans="1:16">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="13">
         <v>13900000029</v>
       </c>
-      <c r="D31" t="s" s="17">
-        <v>144</v>
-      </c>
-      <c r="E31" t="s" s="17">
-        <v>91</v>
-      </c>
-      <c r="F31" s="18">
+      <c r="D31" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="F31" s="13">
         <v>29</v>
       </c>
-      <c r="G31" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H31" s="16"/>
-      <c r="I31" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J31" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K31" s="16"/>
-      <c r="L31" s="16"/>
-      <c r="M31" t="s" s="17">
-        <v>145</v>
-      </c>
-      <c r="N31" t="s" s="20">
-        <v>130</v>
+      <c r="G31" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="11"/>
+      <c r="I31" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J31" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K31" s="11"/>
+      <c r="L31" s="11"/>
+      <c r="M31" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="N31" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="O31" s="21">
         <v>1</v>
       </c>
+      <c r="P31" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="16"/>
-      <c r="B32" t="s" s="17">
-        <v>146</v>
-      </c>
-      <c r="C32" s="18">
+    <row r="32" ht="17" customHeight="1" spans="1:16">
+      <c r="A32" s="11"/>
+      <c r="B32" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="13">
         <v>13900000030</v>
       </c>
-      <c r="D32" t="s" s="17">
-        <v>147</v>
-      </c>
-      <c r="E32" t="s" s="17">
-        <v>96</v>
-      </c>
-      <c r="F32" s="18">
+      <c r="D32" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" s="13">
         <v>30</v>
       </c>
-      <c r="G32" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H32" s="16"/>
-      <c r="I32" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J32" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K32" s="16"/>
-      <c r="L32" s="16"/>
-      <c r="M32" t="s" s="17">
-        <v>148</v>
-      </c>
-      <c r="N32" t="s" s="20">
-        <v>130</v>
+      <c r="G32" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="11"/>
+      <c r="I32" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K32" s="11"/>
+      <c r="L32" s="11"/>
+      <c r="M32" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="N32" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="O32" s="21">
         <v>1</v>
       </c>
+      <c r="P32" s="19">
+        <v>123456</v>
+      </c>
     </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="16"/>
-      <c r="B33" t="s" s="17">
-        <v>149</v>
-      </c>
-      <c r="C33" s="18">
+    <row r="33" ht="17" customHeight="1" spans="1:16">
+      <c r="A33" s="11"/>
+      <c r="B33" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C33" s="13">
         <v>13900000031</v>
       </c>
-      <c r="D33" t="s" s="17">
-        <v>150</v>
-      </c>
-      <c r="E33" t="s" s="17">
-        <v>96</v>
-      </c>
-      <c r="F33" s="18">
+      <c r="D33" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="F33" s="13">
         <v>31</v>
       </c>
-      <c r="G33" t="s" s="17">
-        <v>19</v>
-      </c>
-      <c r="H33" s="16"/>
-      <c r="I33" t="s" s="17">
-        <v>21</v>
-      </c>
-      <c r="J33" t="s" s="17">
-        <v>110</v>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" t="s" s="17">
-        <v>151</v>
-      </c>
-      <c r="N33" t="s" s="20">
-        <v>130</v>
+      <c r="G33" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="11"/>
+      <c r="I33" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J33" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="K33" s="11"/>
+      <c r="L33" s="11"/>
+      <c r="M33" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="N33" s="20" t="s">
+        <v>131</v>
       </c>
       <c r="O33" s="21">
         <v>1</v>
+      </c>
+      <c r="P33" s="19">
+        <v>123456</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
   <pageMargins left="0.699306" right="0.699306" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup paperSize="1" orientation="portrait" useFirstPageNumber="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>

--- a/organization-server/src/main/resources/Import_template.xlsx
+++ b/organization-server/src/main/resources/Import_template.xlsx
@@ -32,7 +32,7 @@
     <t>填表说明：
 1. 千万不要修改表结构，只能填写下面空格和增加行数，不要删除此说明行和表头行，不要删除列和新加列；
 2. 标绿字段为必填项，黑色字段为选填项；
-3. 用户 ID：非必填，成员的唯一标识，可以由字母、数字组成，不填则由系统自动生成，不可重复，用户创建成功后用户 ID无法修改；
+3. 用户 ID：非必填，成员的唯一标识，可以由字母、数字组成，不填则由系统自动生成，不可重复。如果有自己的用户系统，可以填写对应用户ID；否则建议为空自动生成。用户创建成功后用户 ID无法修改；
 4. 手机：必填，且在本企业内不可重复；
 5. 部门：必填，上下级部门间使用“/“隔开，请从最上级部门（即您的公司名）开始填写，例如“XX有限公司/人事部”，若归属于多个部门请用英文逗号隔开；
 6. 性别：请填写男或女；

--- a/organization-server/src/main/resources/Import_template.xlsx
+++ b/organization-server/src/main/resources/Import_template.xlsx
@@ -31,10 +31,10 @@
   <si>
     <t>填表说明：
 1. 千万不要修改表结构，只能填写下面空格和增加行数，不要删除此说明行和表头行，不要删除列和新加列；
-2. 标绿字段为必填项，黑色字段为选填项；
+2. 标红字段为必填项，绿色字段为选填项；
 3. 用户 ID：非必填，成员的唯一标识，可以由字母、数字组成，不填则由系统自动生成，不可重复。如果有自己的用户系统，可以填写对应用户ID；否则建议为空自动生成。用户创建成功后用户 ID无法修改；
 4. 手机：必填，且在本企业内不可重复；
-5. 部门：必填，上下级部门间使用“/“隔开，请从最上级部门（即您的公司名）开始填写，例如“XX有限公司/人事部”，若归属于多个部门请用英文逗号隔开；
+5. 部门：必填，上下级部门间使用“/“隔开，请从最上级部门（即您的公司名）开始填写，例如“XX有限公司/人事部”，若归属于多个部门请用完整路径用英文逗号隔开，多个部门时，部分负责人字段需要一一对应；
 6. 性别：请填写男或女；
 7. 人员类型：请从下列选项中选填一个选项：“正式“、“实习“、“外包“、“劳务“、“顾问“，若不填则默认为“正式“；
 8. 部门负责人：请填入“是“、“否“，若不填则默认为“否“，若归属于多个部门请用英文“,”隔开；
@@ -940,6 +940,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="10"/>
       </left>
@@ -965,15 +974,6 @@
       <bottom style="thin">
         <color indexed="10"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="10"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1235,6 +1235,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1244,35 +1247,32 @@
     <xf numFmtId="49" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" readingOrder="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1402,13 +1402,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/customStorage/customStorage.xml><?xml version="1.0" encoding="utf-8"?>
-<customStorage xmlns="https://web.wps.cn/et/2018/main">
-  <book/>
-  <sheets/>
-</customStorage>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2485,136 +2478,136 @@
       <c r="K1" s="3"/>
       <c r="L1" s="3"/>
       <c r="M1" s="3"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
+      <c r="N1" s="4"/>
+      <c r="O1" s="4"/>
+      <c r="P1" s="4"/>
     </row>
     <row r="2" ht="19.25" customHeight="1" spans="1:16">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O2" s="17" t="s">
+      <c r="O2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="17" t="s">
+      <c r="P2" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="3" ht="16.75" customHeight="1" spans="1:16">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="11">
         <v>13900000001</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="9">
+      <c r="F3" s="11">
         <v>1</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="14" t="s">
+      <c r="H3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="10" t="s">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="18" t="s">
+      <c r="N3" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="15">
         <v>10</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="4" ht="17" customHeight="1" spans="1:16">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="18">
         <v>13900000002</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="18">
         <v>2</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="12" t="s">
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="17" t="s">
         <v>31</v>
       </c>
       <c r="N4" s="20" t="s">
@@ -2623,42 +2616,42 @@
       <c r="O4" s="21">
         <v>8</v>
       </c>
-      <c r="P4" s="19">
+      <c r="P4" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="5" ht="17" customHeight="1" spans="1:16">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="16"/>
+      <c r="B5" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="18">
         <v>13900000003</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="18">
         <v>3</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11"/>
-      <c r="M5" s="12" t="s">
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="17" t="s">
         <v>37</v>
       </c>
       <c r="N5" s="20" t="s">
@@ -2667,42 +2660,42 @@
       <c r="O5" s="21">
         <v>8</v>
       </c>
-      <c r="P5" s="19">
+      <c r="P5" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="6" ht="17" customHeight="1" spans="1:16">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="16"/>
+      <c r="B6" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C6" s="18">
         <v>13900000004</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="18">
         <v>4</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="J6" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="K6" s="11"/>
-      <c r="L6" s="11"/>
-      <c r="M6" s="12" t="s">
+      <c r="K6" s="16"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="17" t="s">
         <v>43</v>
       </c>
       <c r="N6" s="20" t="s">
@@ -2711,42 +2704,42 @@
       <c r="O6" s="21">
         <v>7</v>
       </c>
-      <c r="P6" s="19">
+      <c r="P6" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="7" ht="17" customHeight="1" spans="1:16">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="16"/>
+      <c r="B7" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="18">
         <v>13900000005</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="18">
         <v>5</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="J7" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="11"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="12" t="s">
+      <c r="K7" s="16"/>
+      <c r="L7" s="16"/>
+      <c r="M7" s="17" t="s">
         <v>49</v>
       </c>
       <c r="N7" s="20" t="s">
@@ -2755,40 +2748,40 @@
       <c r="O7" s="21">
         <v>7</v>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="8" ht="17" customHeight="1" spans="1:16">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="16"/>
+      <c r="B8" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="18">
         <v>13900000006</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="18">
         <v>6</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H8" s="11"/>
-      <c r="I8" s="12" t="s">
+      <c r="H8" s="16"/>
+      <c r="I8" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J8" s="12" t="s">
+      <c r="J8" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K8" s="11"/>
-      <c r="L8" s="11"/>
-      <c r="M8" s="12" t="s">
+      <c r="K8" s="16"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="17" t="s">
         <v>55</v>
       </c>
       <c r="N8" s="20" t="s">
@@ -2797,40 +2790,40 @@
       <c r="O8" s="21">
         <v>7</v>
       </c>
-      <c r="P8" s="19">
+      <c r="P8" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="9" ht="17" customHeight="1" spans="1:16">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="16"/>
+      <c r="B9" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C9" s="18">
         <v>13900000007</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="D9" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="18">
         <v>7</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H9" s="11"/>
-      <c r="I9" s="12" t="s">
+      <c r="H9" s="16"/>
+      <c r="I9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="J9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="11"/>
-      <c r="L9" s="11"/>
-      <c r="M9" s="12" t="s">
+      <c r="K9" s="16"/>
+      <c r="L9" s="16"/>
+      <c r="M9" s="17" t="s">
         <v>60</v>
       </c>
       <c r="N9" s="20" t="s">
@@ -2839,40 +2832,40 @@
       <c r="O9" s="21">
         <v>7</v>
       </c>
-      <c r="P9" s="19">
+      <c r="P9" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="10" ht="17" customHeight="1" spans="1:16">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12" t="s">
+      <c r="A10" s="16"/>
+      <c r="B10" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C10" s="18">
         <v>13900000008</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="18">
         <v>8</v>
       </c>
-      <c r="G10" s="12" t="s">
+      <c r="G10" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="11"/>
-      <c r="I10" s="12" t="s">
+      <c r="H10" s="16"/>
+      <c r="I10" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="12" t="s">
+      <c r="J10" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="11"/>
-      <c r="L10" s="11"/>
-      <c r="M10" s="12" t="s">
+      <c r="K10" s="16"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="17" t="s">
         <v>65</v>
       </c>
       <c r="N10" s="20" t="s">
@@ -2881,40 +2874,40 @@
       <c r="O10" s="21">
         <v>3</v>
       </c>
-      <c r="P10" s="19">
+      <c r="P10" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="11" ht="17" customHeight="1" spans="1:16">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12" t="s">
+      <c r="A11" s="16"/>
+      <c r="B11" s="17" t="s">
         <v>67</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C11" s="18">
         <v>13900000009</v>
       </c>
-      <c r="D11" s="12" t="s">
+      <c r="D11" s="17" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="17" t="s">
         <v>69</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="18">
         <v>9</v>
       </c>
-      <c r="G11" s="12" t="s">
+      <c r="G11" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="11"/>
-      <c r="I11" s="12" t="s">
+      <c r="H11" s="16"/>
+      <c r="I11" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J11" s="12" t="s">
+      <c r="J11" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K11" s="11"/>
-      <c r="L11" s="11"/>
-      <c r="M11" s="12" t="s">
+      <c r="K11" s="16"/>
+      <c r="L11" s="16"/>
+      <c r="M11" s="17" t="s">
         <v>70</v>
       </c>
       <c r="N11" s="20" t="s">
@@ -2923,40 +2916,40 @@
       <c r="O11" s="21">
         <v>4</v>
       </c>
-      <c r="P11" s="19">
+      <c r="P11" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="12" ht="17" customHeight="1" spans="1:16">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12" t="s">
+      <c r="A12" s="16"/>
+      <c r="B12" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C12" s="18">
         <v>13900000010</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="18">
         <v>10</v>
       </c>
-      <c r="G12" s="12" t="s">
+      <c r="G12" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H12" s="11"/>
-      <c r="I12" s="12" t="s">
+      <c r="H12" s="16"/>
+      <c r="I12" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J12" s="12" t="s">
+      <c r="J12" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K12" s="11"/>
-      <c r="L12" s="11"/>
-      <c r="M12" s="12" t="s">
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="17" t="s">
         <v>75</v>
       </c>
       <c r="N12" s="20" t="s">
@@ -2965,40 +2958,40 @@
       <c r="O12" s="21">
         <v>4</v>
       </c>
-      <c r="P12" s="19">
+      <c r="P12" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="13" ht="17" customHeight="1" spans="1:16">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C13" s="18">
         <v>13900000011</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="17" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="18">
         <v>11</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H13" s="11"/>
-      <c r="I13" s="12" t="s">
+      <c r="H13" s="16"/>
+      <c r="I13" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J13" s="12" t="s">
+      <c r="J13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="12" t="s">
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="17" t="s">
         <v>80</v>
       </c>
       <c r="N13" s="20" t="s">
@@ -3007,40 +3000,40 @@
       <c r="O13" s="21">
         <v>5</v>
       </c>
-      <c r="P13" s="19">
+      <c r="P13" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="14" ht="17" customHeight="1" spans="1:16">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12" t="s">
+      <c r="A14" s="16"/>
+      <c r="B14" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C14" s="18">
         <v>13900000012</v>
       </c>
-      <c r="D14" s="12" t="s">
+      <c r="D14" s="17" t="s">
         <v>83</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="18">
         <v>12</v>
       </c>
-      <c r="G14" s="12" t="s">
+      <c r="G14" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H14" s="11"/>
-      <c r="I14" s="12" t="s">
+      <c r="H14" s="16"/>
+      <c r="I14" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="J14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
-      <c r="M14" s="12" t="s">
+      <c r="K14" s="16"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="17" t="s">
         <v>85</v>
       </c>
       <c r="N14" s="20" t="s">
@@ -3049,40 +3042,40 @@
       <c r="O14" s="21">
         <v>3</v>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="15" ht="17" customHeight="1" spans="1:16">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12" t="s">
+      <c r="A15" s="16"/>
+      <c r="B15" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C15" s="18">
         <v>13900000013</v>
       </c>
-      <c r="D15" s="12" t="s">
+      <c r="D15" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="18">
         <v>13</v>
       </c>
-      <c r="G15" s="12" t="s">
+      <c r="G15" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="11"/>
-      <c r="I15" s="12" t="s">
+      <c r="H15" s="16"/>
+      <c r="I15" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="12" t="s">
+      <c r="J15" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="12" t="s">
+      <c r="K15" s="16"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="17" t="s">
         <v>89</v>
       </c>
       <c r="N15" s="20" t="s">
@@ -3091,40 +3084,40 @@
       <c r="O15" s="21">
         <v>3</v>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="16" ht="17" customHeight="1" spans="1:16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12" t="s">
+      <c r="A16" s="16"/>
+      <c r="B16" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="C16" s="13">
+      <c r="C16" s="18">
         <v>13900000014</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="18">
         <v>14</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H16" s="11"/>
-      <c r="I16" s="12" t="s">
+      <c r="H16" s="16"/>
+      <c r="I16" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K16" s="11"/>
-      <c r="L16" s="11"/>
-      <c r="M16" s="12" t="s">
+      <c r="K16" s="16"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="17" t="s">
         <v>93</v>
       </c>
       <c r="N16" s="20" t="s">
@@ -3133,40 +3126,40 @@
       <c r="O16" s="21">
         <v>3</v>
       </c>
-      <c r="P16" s="19">
+      <c r="P16" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1" spans="1:16">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12" t="s">
+      <c r="A17" s="16"/>
+      <c r="B17" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="C17" s="13">
+      <c r="C17" s="18">
         <v>13900000015</v>
       </c>
-      <c r="D17" s="12" t="s">
+      <c r="D17" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="18">
         <v>15</v>
       </c>
-      <c r="G17" s="12" t="s">
+      <c r="G17" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H17" s="11"/>
-      <c r="I17" s="12" t="s">
+      <c r="H17" s="16"/>
+      <c r="I17" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="12" t="s">
+      <c r="J17" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="11"/>
-      <c r="L17" s="11"/>
-      <c r="M17" s="12" t="s">
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="17" t="s">
         <v>98</v>
       </c>
       <c r="N17" s="20" t="s">
@@ -3175,40 +3168,40 @@
       <c r="O17" s="21">
         <v>3</v>
       </c>
-      <c r="P17" s="19">
+      <c r="P17" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="18" ht="17" customHeight="1" spans="1:16">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12" t="s">
+      <c r="A18" s="16"/>
+      <c r="B18" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="13">
+      <c r="C18" s="18">
         <v>13900000016</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="18">
         <v>16</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H18" s="11"/>
-      <c r="I18" s="12" t="s">
+      <c r="H18" s="16"/>
+      <c r="I18" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J18" s="12" t="s">
+      <c r="J18" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="12" t="s">
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="17" t="s">
         <v>102</v>
       </c>
       <c r="N18" s="20" t="s">
@@ -3217,40 +3210,40 @@
       <c r="O18" s="21">
         <v>1</v>
       </c>
-      <c r="P18" s="19">
+      <c r="P18" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="19" ht="17" customHeight="1" spans="1:16">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12" t="s">
+      <c r="A19" s="16"/>
+      <c r="B19" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="C19" s="13">
+      <c r="C19" s="18">
         <v>13900000017</v>
       </c>
-      <c r="D19" s="12" t="s">
+      <c r="D19" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="17" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="18">
         <v>17</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H19" s="11"/>
-      <c r="I19" s="12" t="s">
+      <c r="H19" s="16"/>
+      <c r="I19" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J19" s="12" t="s">
+      <c r="J19" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="12" t="s">
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="17" t="s">
         <v>107</v>
       </c>
       <c r="N19" s="20" t="s">
@@ -3259,40 +3252,40 @@
       <c r="O19" s="21">
         <v>1</v>
       </c>
-      <c r="P19" s="19">
+      <c r="P19" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="20" ht="17" customHeight="1" spans="1:16">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12" t="s">
+      <c r="A20" s="16"/>
+      <c r="B20" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="C20" s="13">
+      <c r="C20" s="18">
         <v>13900000018</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="18">
         <v>18</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H20" s="11"/>
-      <c r="I20" s="12" t="s">
+      <c r="H20" s="16"/>
+      <c r="I20" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J20" s="12" t="s">
+      <c r="J20" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K20" s="11"/>
-      <c r="L20" s="11"/>
-      <c r="M20" s="12" t="s">
+      <c r="K20" s="16"/>
+      <c r="L20" s="16"/>
+      <c r="M20" s="17" t="s">
         <v>112</v>
       </c>
       <c r="N20" s="20" t="s">
@@ -3301,40 +3294,40 @@
       <c r="O20" s="21">
         <v>1</v>
       </c>
-      <c r="P20" s="19">
+      <c r="P20" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="21" ht="17" customHeight="1" spans="1:16">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12" t="s">
+      <c r="A21" s="16"/>
+      <c r="B21" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="C21" s="13">
+      <c r="C21" s="18">
         <v>13900000019</v>
       </c>
-      <c r="D21" s="12" t="s">
+      <c r="D21" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="17" t="s">
         <v>110</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="18">
         <v>19</v>
       </c>
-      <c r="G21" s="12" t="s">
+      <c r="G21" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H21" s="11"/>
-      <c r="I21" s="12" t="s">
+      <c r="H21" s="16"/>
+      <c r="I21" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J21" s="12" t="s">
+      <c r="J21" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K21" s="11"/>
-      <c r="L21" s="11"/>
-      <c r="M21" s="12" t="s">
+      <c r="K21" s="16"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="17" t="s">
         <v>115</v>
       </c>
       <c r="N21" s="20" t="s">
@@ -3343,40 +3336,40 @@
       <c r="O21" s="21">
         <v>1</v>
       </c>
-      <c r="P21" s="19">
+      <c r="P21" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="22" ht="17" customHeight="1" spans="1:16">
-      <c r="A22" s="11"/>
-      <c r="B22" s="12" t="s">
+      <c r="A22" s="16"/>
+      <c r="B22" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="18">
         <v>13900000020</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="D22" s="17" t="s">
         <v>117</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="18">
         <v>20</v>
       </c>
-      <c r="G22" s="12" t="s">
+      <c r="G22" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H22" s="11"/>
-      <c r="I22" s="12" t="s">
+      <c r="H22" s="16"/>
+      <c r="I22" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J22" s="12" t="s">
+      <c r="J22" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11"/>
-      <c r="M22" s="12" t="s">
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="17" t="s">
         <v>118</v>
       </c>
       <c r="N22" s="20" t="s">
@@ -3385,40 +3378,40 @@
       <c r="O22" s="21">
         <v>1</v>
       </c>
-      <c r="P22" s="19">
+      <c r="P22" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="23" ht="17" customHeight="1" spans="1:16">
-      <c r="A23" s="11"/>
-      <c r="B23" s="12" t="s">
+      <c r="A23" s="16"/>
+      <c r="B23" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="C23" s="13">
+      <c r="C23" s="18">
         <v>13900000021</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="D23" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="E23" s="12" t="s">
+      <c r="E23" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="18">
         <v>21</v>
       </c>
-      <c r="G23" s="12" t="s">
+      <c r="G23" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H23" s="11"/>
-      <c r="I23" s="12" t="s">
+      <c r="H23" s="16"/>
+      <c r="I23" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J23" s="12" t="s">
+      <c r="J23" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K23" s="11"/>
-      <c r="L23" s="11"/>
-      <c r="M23" s="12" t="s">
+      <c r="K23" s="16"/>
+      <c r="L23" s="16"/>
+      <c r="M23" s="17" t="s">
         <v>121</v>
       </c>
       <c r="N23" s="20" t="s">
@@ -3427,40 +3420,40 @@
       <c r="O23" s="21">
         <v>1</v>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1" spans="1:16">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12" t="s">
+      <c r="A24" s="16"/>
+      <c r="B24" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="18">
         <v>13900000022</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="18">
         <v>22</v>
       </c>
-      <c r="G24" s="12" t="s">
+      <c r="G24" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H24" s="11"/>
-      <c r="I24" s="12" t="s">
+      <c r="H24" s="16"/>
+      <c r="I24" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J24" s="12" t="s">
+      <c r="J24" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
-      <c r="M24" s="12" t="s">
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="M24" s="17" t="s">
         <v>124</v>
       </c>
       <c r="N24" s="20" t="s">
@@ -3469,40 +3462,40 @@
       <c r="O24" s="21">
         <v>1</v>
       </c>
-      <c r="P24" s="19">
+      <c r="P24" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1" spans="1:16">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12" t="s">
+      <c r="A25" s="16"/>
+      <c r="B25" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="C25" s="13">
+      <c r="C25" s="18">
         <v>13900000023</v>
       </c>
-      <c r="D25" s="12" t="s">
+      <c r="D25" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="18">
         <v>23</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H25" s="11"/>
-      <c r="I25" s="12" t="s">
+      <c r="H25" s="16"/>
+      <c r="I25" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
-      <c r="M25" s="12" t="s">
+      <c r="K25" s="16"/>
+      <c r="L25" s="16"/>
+      <c r="M25" s="17" t="s">
         <v>127</v>
       </c>
       <c r="N25" s="20" t="s">
@@ -3511,40 +3504,40 @@
       <c r="O25" s="21">
         <v>1</v>
       </c>
-      <c r="P25" s="19">
+      <c r="P25" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1" spans="1:16">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12" t="s">
+      <c r="A26" s="16"/>
+      <c r="B26" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="C26" s="13">
+      <c r="C26" s="18">
         <v>13900000024</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="D26" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="18">
         <v>24</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H26" s="11"/>
-      <c r="I26" s="12" t="s">
+      <c r="H26" s="16"/>
+      <c r="I26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J26" s="12" t="s">
+      <c r="J26" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
-      <c r="M26" s="12" t="s">
+      <c r="K26" s="16"/>
+      <c r="L26" s="16"/>
+      <c r="M26" s="17" t="s">
         <v>130</v>
       </c>
       <c r="N26" s="20" t="s">
@@ -3553,40 +3546,40 @@
       <c r="O26" s="21">
         <v>1</v>
       </c>
-      <c r="P26" s="19">
+      <c r="P26" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="27" ht="17" customHeight="1" spans="1:16">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12" t="s">
+      <c r="A27" s="16"/>
+      <c r="B27" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="18">
         <v>13900000025</v>
       </c>
-      <c r="D27" s="12" t="s">
+      <c r="D27" s="17" t="s">
         <v>133</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="18">
         <v>25</v>
       </c>
-      <c r="G27" s="12" t="s">
+      <c r="G27" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="11"/>
-      <c r="I27" s="12" t="s">
+      <c r="H27" s="16"/>
+      <c r="I27" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J27" s="12" t="s">
+      <c r="J27" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
-      <c r="M27" s="12" t="s">
+      <c r="K27" s="16"/>
+      <c r="L27" s="16"/>
+      <c r="M27" s="17" t="s">
         <v>134</v>
       </c>
       <c r="N27" s="20" t="s">
@@ -3595,40 +3588,40 @@
       <c r="O27" s="21">
         <v>1</v>
       </c>
-      <c r="P27" s="19">
+      <c r="P27" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="28" ht="17" customHeight="1" spans="1:16">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12" t="s">
+      <c r="A28" s="16"/>
+      <c r="B28" s="17" t="s">
         <v>135</v>
       </c>
-      <c r="C28" s="13">
+      <c r="C28" s="18">
         <v>13900000026</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="18">
         <v>26</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H28" s="11"/>
-      <c r="I28" s="12" t="s">
+      <c r="H28" s="16"/>
+      <c r="I28" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J28" s="12" t="s">
+      <c r="J28" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
-      <c r="M28" s="12" t="s">
+      <c r="K28" s="16"/>
+      <c r="L28" s="16"/>
+      <c r="M28" s="17" t="s">
         <v>137</v>
       </c>
       <c r="N28" s="20" t="s">
@@ -3637,40 +3630,40 @@
       <c r="O28" s="21">
         <v>2</v>
       </c>
-      <c r="P28" s="19">
+      <c r="P28" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="29" ht="17" customHeight="1" spans="1:16">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12" t="s">
+      <c r="A29" s="16"/>
+      <c r="B29" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="C29" s="13">
+      <c r="C29" s="18">
         <v>13900000027</v>
       </c>
-      <c r="D29" s="12" t="s">
+      <c r="D29" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="18">
         <v>27</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H29" s="11"/>
-      <c r="I29" s="12" t="s">
+      <c r="H29" s="16"/>
+      <c r="I29" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J29" s="12" t="s">
+      <c r="J29" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
-      <c r="M29" s="12" t="s">
+      <c r="K29" s="16"/>
+      <c r="L29" s="16"/>
+      <c r="M29" s="17" t="s">
         <v>140</v>
       </c>
       <c r="N29" s="20" t="s">
@@ -3679,40 +3672,40 @@
       <c r="O29" s="21">
         <v>2</v>
       </c>
-      <c r="P29" s="19">
+      <c r="P29" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="30" ht="17" customHeight="1" spans="1:16">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12" t="s">
+      <c r="A30" s="16"/>
+      <c r="B30" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="13">
+      <c r="C30" s="18">
         <v>13900000028</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="D30" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="18">
         <v>28</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="12" t="s">
+      <c r="H30" s="16"/>
+      <c r="I30" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="J30" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="12" t="s">
+      <c r="K30" s="16"/>
+      <c r="L30" s="16"/>
+      <c r="M30" s="17" t="s">
         <v>143</v>
       </c>
       <c r="N30" s="20" t="s">
@@ -3721,40 +3714,40 @@
       <c r="O30" s="21">
         <v>1</v>
       </c>
-      <c r="P30" s="19">
+      <c r="P30" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="31" ht="17" customHeight="1" spans="1:16">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12" t="s">
+      <c r="A31" s="16"/>
+      <c r="B31" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="C31" s="13">
+      <c r="C31" s="18">
         <v>13900000029</v>
       </c>
-      <c r="D31" s="12" t="s">
+      <c r="D31" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="E31" s="12" t="s">
+      <c r="E31" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="18">
         <v>29</v>
       </c>
-      <c r="G31" s="12" t="s">
+      <c r="G31" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="12" t="s">
+      <c r="H31" s="16"/>
+      <c r="I31" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J31" s="12" t="s">
+      <c r="J31" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
-      <c r="M31" s="12" t="s">
+      <c r="K31" s="16"/>
+      <c r="L31" s="16"/>
+      <c r="M31" s="17" t="s">
         <v>146</v>
       </c>
       <c r="N31" s="20" t="s">
@@ -3763,40 +3756,40 @@
       <c r="O31" s="21">
         <v>1</v>
       </c>
-      <c r="P31" s="19">
+      <c r="P31" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="32" ht="17" customHeight="1" spans="1:16">
-      <c r="A32" s="11"/>
-      <c r="B32" s="12" t="s">
+      <c r="A32" s="16"/>
+      <c r="B32" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="C32" s="13">
+      <c r="C32" s="18">
         <v>13900000030</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="18">
         <v>30</v>
       </c>
-      <c r="G32" s="12" t="s">
+      <c r="G32" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="12" t="s">
+      <c r="H32" s="16"/>
+      <c r="I32" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J32" s="12" t="s">
+      <c r="J32" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
-      <c r="M32" s="12" t="s">
+      <c r="K32" s="16"/>
+      <c r="L32" s="16"/>
+      <c r="M32" s="17" t="s">
         <v>149</v>
       </c>
       <c r="N32" s="20" t="s">
@@ -3805,40 +3798,40 @@
       <c r="O32" s="21">
         <v>1</v>
       </c>
-      <c r="P32" s="19">
+      <c r="P32" s="15">
         <v>123456</v>
       </c>
     </row>
     <row r="33" ht="17" customHeight="1" spans="1:16">
-      <c r="A33" s="11"/>
-      <c r="B33" s="12" t="s">
+      <c r="A33" s="16"/>
+      <c r="B33" s="17" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="13">
+      <c r="C33" s="18">
         <v>13900000031</v>
       </c>
-      <c r="D33" s="12" t="s">
+      <c r="D33" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="18">
         <v>31</v>
       </c>
-      <c r="G33" s="12" t="s">
+      <c r="G33" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="12" t="s">
+      <c r="H33" s="16"/>
+      <c r="I33" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J33" s="12" t="s">
+      <c r="J33" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
-      <c r="M33" s="12" t="s">
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="17" t="s">
         <v>152</v>
       </c>
       <c r="N33" s="20" t="s">
@@ -3847,7 +3840,7 @@
       <c r="O33" s="21">
         <v>1</v>
       </c>
-      <c r="P33" s="19">
+      <c r="P33" s="15">
         <v>123456</v>
       </c>
     </row>
